--- a/forms/trg/Formulir_TRG_bus-trans.xlsx
+++ b/forms/trg/Formulir_TRG_bus-trans.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,20 +913,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Try Dharsana</t>
+          <t>Prof. Dr. Mursalim Nohong, S.E., M.Si., CWM®.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Financial Management</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -934,12 +934,12 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6789754</t>
+          <t>5989806</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>59233713000</t>
+          <t>57202267173</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Sabbar Dahham Sabbar</t>
+          <t>Muhammad Try Dharsana</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -975,12 +975,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6863841</t>
+          <t>6789754</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>58155587300</t>
+          <t>59233713000</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Amer Ahmad Hatamleh</t>
+          <t>Sabbar Dahham Sabbar</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Irbid National University, Jordan</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="n"/>
@@ -1013,15 +1013,15 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-1847-0492</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6863841</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57219198640</t>
+          <t>58155587300</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Nur Alamzah</t>
+          <t>Amer Ahmad Hatamleh</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Irbid National University, Jordan</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1054,13 +1054,17 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>6869782</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1847-0492</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57219198640</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1073,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Fakhrul Indra Hermansyah</t>
+          <t>Nur Alamzah</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1094,14 +1098,10 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6885421</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>59232685400</t>
-        </is>
-      </c>
+          <t>6869782</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Andi Iqra Pradipta Natsir</t>
+          <t>Fakhrul Indra Hermansyah</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1135,10 +1135,14 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6783521</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+          <t>6885421</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>59232685400</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1151,12 +1155,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Zakiyyah Mutiah</t>
+          <t>Andi Iqra Pradipta Natsir</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1170,7 +1174,11 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6783521</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
@@ -1184,12 +1192,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Ibriati Kartika Alimuddin</t>
+          <t>Zakiyyah Mutiah</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1202,21 +1210,9 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-8493-1034</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6660437</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>57977227500</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1229,12 +1225,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Bahtiar Herman</t>
+          <t>Ibriati Kartika Alimuddin</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1247,9 +1243,21 @@
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8493-1034</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6660437</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>57977227500</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1262,12 +1270,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Fauziyyah Mutiah</t>
+          <t>Bahtiar Herman</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1293,10 +1301,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Fauziyyah Mutiah</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Business Transformation Thematic Research Group explores how companies can adapt and thrive in the digital age. We research technology, organizational culture, leadership, sustainable business practices while promoting green financial management to develop innovative change strategies and enhancing competitiveness in the global economy.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1304,7 +1328,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1493,15 +1521,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
